--- a/Hoàng/2025/T5/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA- CHI NHÁNH QUẢNG NAM T5-2025 BS Long đã duyệt.xlsx
+++ b/Hoàng/2025/T5/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)/TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA- CHI NHÁNH QUẢNG NAM T5-2025 BS Long đã duyệt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\TỔNG CÔNG TY CỔ PHẦN BẢO HIỂM AAA - CHI NHÁNH QUẢNG NAM (83-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C11B620-313E-4BBA-8A72-D746DD6B6187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74F65A-E28A-4DD4-85ED-0C75567D83C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KQCN" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">KQCN!$A$2:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$9:$W$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$B$9:$X$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">Sheet1!$8:$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="196">
   <si>
     <t>CÔNG TY CỔ PHẦN BỆNH VIỆN THIỆN NHÂN ĐÀ NẴNG</t>
   </si>
@@ -747,6 +748,9 @@
 _ Mang kính phù hợp 
 _ Điều trị nha khoa 
 _ Kiểm tra sức khỏe định kỳ </t>
+  </si>
+  <si>
+    <t>SL</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1035,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1071,9 +1075,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1089,9 +1090,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1099,9 +1097,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1120,6 +1115,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1138,29 +1157,32 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1340,13 +1362,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>73959</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>4294</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>7284</xdr:rowOff>
@@ -1414,14 +1436,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>1647825</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>4384</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
@@ -1464,14 +1486,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>247651</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1186959</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
@@ -1809,51 +1831,51 @@
     <col min="2" max="2" width="9.28515625" style="12" customWidth="1"/>
     <col min="3" max="3" width="31.42578125" style="13" customWidth="1"/>
     <col min="4" max="5" width="7.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="22" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="21" customWidth="1"/>
     <col min="7" max="7" width="47.42578125" style="14" customWidth="1"/>
     <col min="8" max="8" width="43" style="15" customWidth="1"/>
     <col min="9" max="9" width="8" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:9" s="18" customFormat="1" ht="181.5" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
@@ -1862,7 +1884,7 @@
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="24" t="s">
         <v>45</v>
       </c>
       <c r="D3" s="10">
@@ -1891,7 +1913,7 @@
       <c r="B4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="D4" s="10">
@@ -1920,7 +1942,7 @@
       <c r="B5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="24" t="s">
         <v>47</v>
       </c>
       <c r="D5" s="10">
@@ -1949,7 +1971,7 @@
       <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="24" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="10">
@@ -1978,7 +2000,7 @@
       <c r="B7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="25" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="10">
@@ -2005,7 +2027,7 @@
       <c r="B8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="25" t="s">
         <v>50</v>
       </c>
       <c r="D8" s="10">
@@ -2034,7 +2056,7 @@
       <c r="B9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>51</v>
       </c>
       <c r="D9" s="10">
@@ -2063,7 +2085,7 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="10">
@@ -2085,14 +2107,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="30" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="27" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="24" t="s">
         <v>53</v>
       </c>
       <c r="D11" s="10">
@@ -2121,7 +2143,7 @@
       <c r="B12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="24" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="10">
@@ -2150,7 +2172,7 @@
       <c r="B13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="24" t="s">
         <v>55</v>
       </c>
       <c r="D13" s="10">
@@ -2179,7 +2201,7 @@
       <c r="B14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="25" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="10">
@@ -2208,7 +2230,7 @@
       <c r="B15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="24" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="10">
@@ -2231,61 +2253,61 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
     </row>
     <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="24"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="23"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="24"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="23"/>
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
     <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="24"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="23"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
     <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="24"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="23"/>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27"/>
@@ -2316,744 +2338,811 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" style="13" customWidth="1"/>
-    <col min="4" max="5" width="7.28515625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="22" customWidth="1"/>
-    <col min="7" max="11" width="8.85546875" style="12" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" style="12" customWidth="1"/>
-    <col min="13" max="18" width="13.5703125" style="12" customWidth="1"/>
-    <col min="19" max="19" width="47.42578125" style="14" customWidth="1"/>
-    <col min="20" max="20" width="43" style="15" customWidth="1"/>
-    <col min="21" max="21" width="8" style="12" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" style="7" customWidth="1"/>
-    <col min="23" max="23" width="18.7109375" style="7" customWidth="1"/>
+    <col min="1" max="2" width="6.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="12" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="21" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="12" customWidth="1"/>
+    <col min="9" max="11" width="8.85546875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="22" style="12" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="12" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" style="12" customWidth="1"/>
+    <col min="16" max="19" width="13.5703125" style="12" customWidth="1"/>
+    <col min="20" max="20" width="47.42578125" style="14" customWidth="1"/>
+    <col min="21" max="21" width="43" style="15" customWidth="1"/>
+    <col min="22" max="22" width="8" style="12" customWidth="1"/>
+    <col min="23" max="23" width="10.7109375" style="7" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="18.7109375" style="7" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1"/>
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="2"/>
-    </row>
-    <row r="2" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="2"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A2"/>
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A3"/>
+      <c r="B3" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A4"/>
+      <c r="B4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="45"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A5"/>
+      <c r="B5" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="44" t="s">
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A6"/>
+      <c r="B6" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="4"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
       <c r="W6" s="4"/>
-    </row>
-    <row r="7" spans="1:23" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="49" t="s">
+      <c r="X6" s="4"/>
+    </row>
+    <row r="7" spans="1:24" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A7"/>
+      <c r="B7" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="5"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
       <c r="W7" s="5"/>
-    </row>
-    <row r="8" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="X7" s="5"/>
+    </row>
+    <row r="8" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="C8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="D8" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E8" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="F8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="G8" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="H8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="36" t="s">
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="31" t="s">
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="T8" s="31" t="s">
+      <c r="U8" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="31" t="s">
+      <c r="V8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="V8" s="47" t="s">
+      <c r="W8" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="W8" s="42" t="s">
+      <c r="X8" s="33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="6" t="s">
+    <row r="9" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="N9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="O9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="Q9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="S9" s="32"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="43"/>
-    </row>
-    <row r="10" spans="1:23" s="18" customFormat="1" ht="181.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="29">
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="34"/>
+    </row>
+    <row r="10" spans="1:24" s="18" customFormat="1" ht="262.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="47">
+        <v>1</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="D10" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="10">
+      <c r="E10" s="10">
         <v>1983</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N10" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="Q10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="8" t="s">
+      <c r="R10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="9"/>
+      <c r="T10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="U10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="V10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="W10" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="W10" s="9" t="s">
+      <c r="X10" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="18" customFormat="1" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
+    <row r="11" spans="1:24" s="18" customFormat="1" ht="321" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
         <v>2</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="47">
+        <v>2</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="D11" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="10">
+      <c r="E11" s="10">
         <v>1979</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="K11" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="L11" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="M11" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="N11" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="R11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="8" t="s">
+      <c r="S11" s="9"/>
+      <c r="T11" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="U11" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="V11" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="V11" s="9" t="s">
+      <c r="W11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="W11" s="9" t="s">
+      <c r="X11" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29">
+    <row r="12" spans="1:24" s="18" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="47">
         <v>3</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="47">
+        <v>3</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="D12" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="10">
+      <c r="E12" s="10">
         <v>1987</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="9">
+      <c r="H12" s="9">
         <v>161</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>60</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="9">
         <v>86</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="M12" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P12" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="8" t="s">
+      <c r="R12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" s="9"/>
+      <c r="T12" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="T12" s="8" t="s">
+      <c r="U12" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="V12" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="V12" s="9" t="s">
+      <c r="W12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="W12" s="28" t="s">
+      <c r="X12" s="26" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="18" customFormat="1" ht="231" x14ac:dyDescent="0.25">
-      <c r="A13" s="29">
+    <row r="13" spans="1:24" s="18" customFormat="1" ht="264" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
         <v>4</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="47">
+        <v>4</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="D13" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="10">
+      <c r="E13" s="10">
         <v>1968</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="L13" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="N13" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="P13" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="Q13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="9"/>
-      <c r="S13" s="8" t="s">
+      <c r="R13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" s="9"/>
+      <c r="T13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="T13" s="8" t="s">
+      <c r="U13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="U13" s="9" t="s">
+      <c r="V13" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="V13" s="9" t="s">
+      <c r="W13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="W13" s="9" t="s">
+      <c r="X13" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="18" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+    <row r="14" spans="1:24" s="18" customFormat="1" ht="99" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47">
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="10">
-        <v>1976</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="B14" s="47">
+        <v>6</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1985</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="H14" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S14" s="9"/>
       <c r="T14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-    </row>
-    <row r="15" spans="1:23" s="18" customFormat="1" ht="99" x14ac:dyDescent="0.25">
-      <c r="A15" s="29">
-        <v>6</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1985</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>62</v>
+        <v>114</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" s="18" customFormat="1" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47">
+        <v>5</v>
+      </c>
+      <c r="B15" s="47">
+        <v>7</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1986</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M15" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="N15" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="O15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="O15" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="8" t="s">
-        <v>114</v>
+      <c r="R15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="U15" s="9" t="s">
-        <v>116</v>
+        <v>125</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" s="18" customFormat="1" ht="132" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
-        <v>7</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1986</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" s="18" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="47">
+        <v>6</v>
+      </c>
+      <c r="B16" s="47">
+        <v>8</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1985</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L16" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="9" t="s">
-        <v>190</v>
-      </c>
       <c r="N16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="P16" s="9" t="s">
         <v>66</v>
@@ -3062,602 +3151,514 @@
         <v>66</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>125</v>
+        <v>66</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="U16" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" s="18" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="29">
-        <v>8</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="10">
-        <v>1985</v>
-      </c>
-      <c r="E17" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="27" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="47">
+        <v>7</v>
+      </c>
+      <c r="B17" s="47">
+        <v>9</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1980</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L17" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M17" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="N17" s="9" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="Q17" s="9" t="s">
         <v>66</v>
       </c>
       <c r="R17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="S17" s="8" t="s">
-        <v>136</v>
+        <v>66</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>92</v>
+        <v>193</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="V17" s="9" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="W17" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" s="30" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>9</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="10">
+        <v>128</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" s="18" customFormat="1" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="47">
+        <v>8</v>
+      </c>
+      <c r="B18" s="47">
+        <v>10</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="10">
         <v>1980</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="H18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>71</v>
-      </c>
       <c r="J18" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="L18" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M18" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="N18" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="O18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="O18" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="P18" s="9" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="Q18" s="9" t="s">
         <v>66</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>193</v>
+        <v>66</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>78</v>
+        <v>153</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="W18" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" s="18" customFormat="1" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
-        <v>10</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="10">
-        <v>1980</v>
-      </c>
-      <c r="E19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" s="18" customFormat="1" ht="191.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="47">
+        <v>9</v>
+      </c>
+      <c r="B19" s="47">
+        <v>11</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1984</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="H19" s="9" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="Q19" s="9" t="s">
         <v>66</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="S19" s="8" t="s">
-        <v>153</v>
+        <v>66</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="U19" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="V19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="V19" s="9" t="s">
-        <v>79</v>
-      </c>
       <c r="W19" s="9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" s="18" customFormat="1" ht="181.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
+        <v>117</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" s="18" customFormat="1" ht="82.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="47">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="10">
-        <v>1984</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="B20" s="47">
+        <v>12</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1989</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>156</v>
-      </c>
       <c r="H20" s="9" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>161</v>
+        <v>66</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="Q20" s="9" t="s">
         <v>66</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>164</v>
+        <v>66</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="U20" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="V20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="V20" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="W20" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" s="18" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="29">
+        <v>79</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" s="18" customFormat="1" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="47">
+        <v>10</v>
+      </c>
+      <c r="B21" s="47">
+        <v>13</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1994</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="9">
+        <v>156</v>
+      </c>
+      <c r="I21" s="9">
+        <v>43</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K21" s="9">
+        <v>109</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="T21" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="V21" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="W21" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="X21" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="50"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="53"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="53"/>
+      <c r="W22" s="53"/>
+      <c r="X22" s="55"/>
+    </row>
+    <row r="23" spans="1:24" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="P23" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A24"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="10">
-        <v>1989</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="R21" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="S21" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="U21" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="V21" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W21" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" s="18" customFormat="1" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="10">
-        <v>1994</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="9">
-        <v>156</v>
-      </c>
-      <c r="H22" s="9">
-        <v>43</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" s="9">
-        <v>109</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="U22" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="V22" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="W22" s="28" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="25">
-        <f>COUNTA(C10:C22)</f>
-        <v>13</v>
-      </c>
-      <c r="D23" s="25">
-        <f t="shared" ref="D23:W23" si="0">COUNTA(D10:D22)</f>
-        <v>13</v>
-      </c>
-      <c r="E23" s="25">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="F23" s="25">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="H23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="J23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="K23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="L23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="M23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="N23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="O23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="P23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="Q23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="R23" s="25">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="S23" s="25">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="T23" s="25">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="U23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="V23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="W23" s="25">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="O24" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="11"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
       <c r="W24" s="11"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="11"/>
+      <c r="X24" s="11"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="W25" s="11"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="V26" s="11"/>
+      <c r="X25" s="11"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="W26" s="11"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="V27" s="11"/>
+      <c r="X26" s="11"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="W27" s="11"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="V28" s="11"/>
+      <c r="X27" s="11"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="W28" s="11"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="V29" s="11"/>
+      <c r="X28" s="11"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="23"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="R29"/>
+      <c r="S29"/>
+      <c r="T29"/>
+      <c r="U29"/>
+      <c r="V29"/>
       <c r="W29" s="11"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" s="11"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="24"/>
-      <c r="G30"/>
+      <c r="B30"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="23"/>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
@@ -3672,17 +3673,18 @@
       <c r="S30"/>
       <c r="T30"/>
       <c r="U30"/>
-      <c r="V30" s="11"/>
+      <c r="V30"/>
       <c r="W30" s="11"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" s="11"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="24"/>
-      <c r="G31"/>
+      <c r="B31"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="23"/>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
@@ -3697,90 +3699,68 @@
       <c r="S31"/>
       <c r="T31"/>
       <c r="U31"/>
-      <c r="V31" s="11"/>
+      <c r="V31"/>
       <c r="W31" s="11"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="24"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-      <c r="S32"/>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A35"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="24"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
+      <c r="X31" s="11"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A34"/>
+      <c r="B34"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="23"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="P24:V24"/>
+    <mergeCell ref="P23:V23"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="B6:V6"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="B2:V2"/>
+    <mergeCell ref="B3:V3"/>
+    <mergeCell ref="B4:V4"/>
+    <mergeCell ref="B5:V5"/>
     <mergeCell ref="W8:W9"/>
-    <mergeCell ref="A6:U6"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:U5"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="A7:U7"/>
-    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="B7:V7"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="U8:U9"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="L8:R8"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="V8:V9"/>
   </mergeCells>
-  <conditionalFormatting sqref="C10:C22">
-    <cfRule type="duplicateValues" dxfId="0" priority="3" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D10:D22">
+    <cfRule type="duplicateValues" dxfId="0" priority="4" stopIfTrue="1"/>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.35433070866141736" right="0.11811023622047245" top="0.24" bottom="0.17" header="0.23" footer="0.17"/>
+  <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
